--- a/user_data.xlsx
+++ b/user_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\github\20251R0136COSE47101\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAABCE0B-4838-4C2D-AC67-EA100BBFA1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310A0DBE-E670-41C0-9C63-9A9E07903710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>자료구조</t>
   </si>
@@ -33,17 +33,852 @@
     <t>알고리즘, 논리설계, 계산이론, 이산수학</t>
   </si>
   <si>
-    <t>프로그래밍언어, 컴퓨터구조, 소프트웨어공학, 데이터베이스, 컴퓨터네트워크</t>
-  </si>
-  <si>
-    <t>인터넷프로토콜, 운영체제, 소프트웨어보안, 데이터과학, 컴퓨터그래픽스</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프로그래밍언어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>컴퓨터구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소프트웨어공학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터베이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>컴퓨터네트워크</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인터넷프로토콜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>운영체제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소프트웨어보안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터과학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>컴퓨터그래픽스</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타임스탬프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컴퓨터학과 전공생이십니까?
+(복수전공, 이중전공, 융합전공, 부전공 포함)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1학년 1학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1학년 2학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2학년 1학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2학년 2학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3학년 1학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3학년 2학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4학년 1학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4학년 2학기에 들은 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터학과 전공 과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 모두 적어주세요. (쉼표로 구분)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1-1. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>자료구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>알고리즘을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1-2. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>자료구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">나 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>알고리즘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>다른 전공강의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>를 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2-1. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>논리설계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>를 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2-2. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터구조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>운영체제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>를 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2-3. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>운영체제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>시스템프로그래밍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3-1. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>인공지능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>딥러닝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>을 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3-2. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>인공지능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>기계학습을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4-1. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>계산이론</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>프로그래밍언어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>를 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4-2. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>프로그래밍언어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴파일러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>를 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5-1. 반드시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>데이터통신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 이후에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>컴퓨터네트워크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>를 수강할 것을 추천하시나요?</t>
+    </r>
+  </si>
+  <si>
+    <t>그 외에도 선수과목이 있다고 생각되는 과목에 대해 자유롭게 적어 주세요. (ex. 딥러닝을 듣고 자연어처리를 들어야 한다)</t>
+  </si>
+  <si>
+    <t>상품 추첨에 참여하실 경우 전화번호를 적어 주세요! (ex. 010-1234-5678)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,16 +893,63 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5B3F86"/>
+        <bgColor rgb="FF5B3F86"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -75,12 +957,84 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF5B3F86"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF5B3F86"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF5B3F86"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF442F65"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -361,26 +1315,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:E1"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="63.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="63.296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B1" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="D2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
